--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Healthfirst</t>
+          <t>Kentro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Azure, Data Factory, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7642aa199d34181</t>
+          <t>https://www.indeed.com/viewjob?jk=f93bd43dc6dfa898</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior . Net Backend Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Healthfirst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7642aa199d34181</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Remote Snowflake Certified Architect / Senior Developer</t>
+          <t>Senior . Net Backend Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MindBoard</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,54 +566,54 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Integrated Services Data Warehouse (ISDW)</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, PySpark, Scala, NoSQL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddd78ed591d456c</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17ae40788e4ec77</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Infrastructure Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39543365ea36fd4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Oracle</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, ETL, ELT, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e904a72543c1613d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e904a72543c1613d</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25f2bc3af4f99176</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
@@ -2008,25 +2008,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,172 +2036,172 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40366659a6fa8e3</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded520dfbe232fda</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Quality Assurance Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, API Gateway, RDS, Azure, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7216e95a38186a</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (GCP)</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>IAM, RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058f81d6a76ddba5</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,102 +2876,102 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Enterprise Software Architect</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06836dacb6415fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5645664d20b6d934</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,102 +3856,102 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b97ef9ad96dfc39</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,40 +3996,2175 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Buildertrend</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Engineer III - Python, Databricks</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LEADER BANK</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Arlington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Orion180 Insurance Services, LLC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Watertown, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI Accelerated Senior Java Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Fiserv</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Berkeley Heights, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>MeridianLink</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Full-Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>The Hearst Corporation</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Troy, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Applications Systems</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>White &amp; Case</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Blockchain Developer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Customer Success Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Britive</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Enterprise Operations Software Internship</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bestow</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Database Engineer II</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Alexandria, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Global Dining</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>.NET Developer-Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>.NET Developer-Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>.NET Developer-Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Data Solutions Developer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sherwin-Williams</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Find the work that fits.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Roadrunner</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Downers Grove, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Software Engineer 2 (AI/GenAI)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Earth City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sr. System Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Woonsocket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Woonsocket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Full Stack Quantitative Developer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SAKSOFT</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Sr. DNS Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>The Evolvers Group</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Gigapower</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Informatics Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Prime Medicine</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Azure Data Engineer - State National</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Markel Corporation</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Bedford, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Janus Henderson Investors</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Business Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Foxconn Industrial Internet - FII</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MuleSoft QA Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Data Platform Architect</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MuleSoft Developer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - App Reliability</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Database and Applications Developer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Lynker</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Pascagoula, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Family Dollar</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Chesapeake, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - App Reliability</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - EMC Life</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EMC Insurance</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>Data Scientist III</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Teladoc Health</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D164" t="n">
         <v>10.4</v>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, ETL, ELT, Microsoft SSIS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, ETL, ELT, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e904a72543c1613d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e904a72543c1613d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,87 +3916,87 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer IV – Web/Database Development</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>ActioNet</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>VHB</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Watertown, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
@@ -4318,17 +4318,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Senior Engineer, Applications Systems</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
@@ -4738,17 +4738,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,24 +4896,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Roadrunner</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf910bfe5104518f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,15 +6156,50 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Teladoc Health</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
           <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e904a72543c1613d</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,59 +3786,59 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer IV – Web/Database Development</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ActioNet</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=283cba6a8ee893ac</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
@@ -4668,25 +4668,25 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Database Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Roadrunner</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbe911be786d31a</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
         </is>
       </c>
     </row>
@@ -6173,17 +6173,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,15 +6191,50 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Teladoc Health</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
           <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,12 +1413,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
@@ -4178,17 +4178,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Hardware Engineer, Design Concept Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
         </is>
       </c>
     </row>
@@ -4423,17 +4423,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Engineer, Applications Systems</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,19 +4521,19 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
@@ -4948,17 +4948,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
@@ -5123,17 +5123,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
@@ -5788,17 +5788,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
@@ -6208,17 +6208,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,15 +6226,50 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Teladoc Health</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
           <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, ETL, ELT, Microsoft SSIS</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Databricks Resident Solution Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
         </is>
       </c>
     </row>
@@ -1693,25 +1693,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,42 +3786,42 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
@@ -3933,17 +3933,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,52 +3986,52 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Hardware Engineer, Design Concept Engineering</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Hardware Engineer, Design Concept Engineering</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Engineer, Applications Systems</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,19 +4556,19 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,59 +4731,59 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Database Engineer II</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, HDFS, Scala, Snowflake, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8531d4cc2132548</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
@@ -6208,17 +6208,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,17 +6226,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
         </is>
       </c>
     </row>
@@ -6272,6 +6272,41 @@
       <c r="G167" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Business Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Foxconn Industrial Internet - FII</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Integration Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Dauch</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
         </is>
       </c>
     </row>
@@ -1518,17 +1518,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Resident Solution Architect</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Resident Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,87 +4021,87 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Hardware Engineer, Design Concept Engineering</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Hardware Engineer, Design Concept Engineering</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Senior Engineer, Applications Systems</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,67 +4766,67 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,32 +5711,32 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,32 +5746,32 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,29 +6051,29 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Security Automation Engineer (Python)</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Cloud Architect</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,7 +6306,112 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Family Dollar</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Chesapeake, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Teladoc Health</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Security Automation Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>MarLabs</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G171"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,17 +3916,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,42 +4091,42 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,59 +4136,59 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,19 +4206,19 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Hardware Engineer, Design Concept Engineering</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Hardware Engineer, Design Concept Engineering</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Engineer, Applications Systems</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,59 +4871,59 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,32 +5781,32 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,67 +5816,67 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Full Stack Quantitative Developer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>SAKSOFT</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,19 +6376,19 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Security Automation Engineer (Python)</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6401,17 +6401,122 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>J2B GLOBAL LLC</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Security Automation Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>MarLabs</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Data Scientist III</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Teladoc Health</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Trupanion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>PayIt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Databricks Resident Solution Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Resident Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e9aa9aff1abc0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,129 +3716,129 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,112 +4021,112 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,59 +4136,59 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a58275a555dc05c</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Hardware Engineer, Design Concept Engineering</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d84adb926e0d21f</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Engineer, Applications Systems</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,19 +4521,19 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,137 +4766,137 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
         </is>
       </c>
     </row>
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,42 +5771,42 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,94 +5816,94 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SAKSOFT</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90fd4a5e897af711</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Senior Azure Data Engineer - State National</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Markel Corporation</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Bedford, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>Janus Henderson Investors</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Janus Henderson Investors</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,24 +6156,24 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,19 +6376,19 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cloud Architect</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6445,76 +6445,6 @@
         </is>
       </c>
       <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb35643e47a7e41b</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Security Automation Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>MarLabs</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Data Scientist III</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Teladoc Health</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trupanion</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f426b92d0adc5e27</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Resident Solution Architect</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Databricks Resident Solution Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,59 +3716,59 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
@@ -4031,42 +4031,42 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LEADER BANK</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Arlington, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,42 +4231,42 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e1ce2b5bd665f69</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Senior Engineer, Applications Systems</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>White &amp; Case</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,59 +4696,59 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,24 +5036,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Kafka, Databricks Lakehouse, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,49 +5501,49 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5553,50 +5553,50 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,54 +5711,54 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5767,38 +5767,38 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer - State National</t>
+          <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Markel Corporation</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bedford, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,402 +6051,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Scala, SQL Server, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=346bc6d60e2f1b8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Janus Henderson Investors</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, dbt, CI/CD, Azure DevOps, Airflow</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6e0919b528bf52</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Full Stack Application Developer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Arctiq</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Data Platform Architect</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Database and Applications Developer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Lynker</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Pascagoula, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - App Reliability</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - App Reliability</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - EMC Life</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>EMC Insurance</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Family Dollar</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Chesapeake, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Security Automation Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>MarLabs</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Data Scientist III</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Teladoc Health</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=720c45a82f53f263</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Integration Specialist</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dauch</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Synapse Analytics, GCP, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034c1e07736ca22b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PayIt</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,29 +1536,29 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Snowflake, MongoDB, NoSQL, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b84daac08f9aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Databricks Resident Solution Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Resident Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Enterprise Architect (San Jose, CA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Blue Acorn iCi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,42 +3716,42 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,17 +3986,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
@@ -4493,17 +4493,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Customer Success Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Britive</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,17 +4966,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Infrastructure Test Engineer, DevOps</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,19 +5221,19 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,42 +5421,42 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
         </is>
       </c>
     </row>
@@ -5683,17 +5683,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, PostgreSQL, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,24 +5736,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Data Scientist III</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>Teladoc Health</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,50 +6016,15 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Security Automation Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>MarLabs</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Remote Snowflake Certified Architect / Senior Developer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MindBoard</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,33 +587,33 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a320d4298f99f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,54 +1441,54 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Databricks Resident Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
         </is>
       </c>
     </row>
@@ -1623,70 +1623,70 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Resident Solution Architect</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise Architect (San Jose, CA)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Blue Acorn iCi</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295cd334b55e1ae2</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quantic</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2960b1e2ceb9f1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3667,73 +3667,73 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,42 +4021,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,52 +4196,52 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
@@ -4423,17 +4423,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Engineer, Applications Systems</t>
+          <t>Business Systems Sr. Analyst</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>White &amp; Case</t>
+          <t>MFS Investment Management</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hive, Scala, Snowflake, Informatica PowerCenter, Oracle, ETL, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6f514e1c4749378</t>
+          <t>https://www.indeed.com/viewjob?jk=bffe2beaec8e627c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>SugarAI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,17 +4896,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,17 +4966,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,19 +5186,19 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Test Engineer, DevOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc739f28a9dbd6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
@@ -5543,17 +5543,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d58ecae6d6b2220</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
@@ -5963,17 +5963,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Scientist III</t>
+          <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Teladoc Health</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,50 +5981,15 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, NoSQL, Tableau, MLOps, Git, Python, SQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14b6367d34339931</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Security Automation Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>MarLabs</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior . Net Backend Software Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,64 +556,64 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=79d27925e100760a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior . Net Backend Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
+          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Remote Snowflake Certified Architect / Senior Developer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MindBoard</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,33 +622,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,54 +1441,54 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Resident Solution Architect</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b239f5e5b3b54a</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,59 +3611,59 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>DEVOPS CLOUD ENGINEER</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,42 +4021,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=0629f04d1d0f4e56</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
         </is>
       </c>
     </row>
@@ -4078,12 +4078,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,59 +4196,59 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4258,15 +4258,15 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,59 +4276,59 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Business Systems Sr. Analyst</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MFS Investment Management</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hive, Scala, Snowflake, Informatica PowerCenter, Oracle, ETL, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bffe2beaec8e627c</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Full-Stack Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>The Hearst Corporation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,59 +4661,59 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Databricks</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SugarAI</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, SQL Server, PostgreSQL, ETL</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9f3319ba4d14a4</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Data Solutions Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Family Dollar</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Chesapeake, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Security Automation Engineer (Python)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,15 +5981,50 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Security Automation Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MarLabs</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Remote Snowflake Certified Architect / Senior Developer</t>
+          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MindBoard</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,46 +657,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
+          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,172 +741,172 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>CNA National Warranty Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f38f6a5da241519e</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b17a26ef65d0fb</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mapout Digital Solutions Inc,</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,129 +3611,129 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,29 +3846,29 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DEVOPS CLOUD ENGINEER</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0629f04d1d0f4e56</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,69 +4056,69 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>S3, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6dfe786d11af63</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,104 +4301,104 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Full Stack Engineer – POS</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Azure, Databricks, Spark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,42 +4686,42 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,59 +4731,59 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,17 +5001,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
@@ -5228,17 +5228,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2389ccbb1e201011</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Sr. System Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,67 +5361,67 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Recruitics_CH Robinson_Sponsored Jobs_East_Maverick</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c02b5052ff31c41</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Solutions Developer</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Oracle, PostgreSQL, Dimensional Modeling, ETL, ELT</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,59 +5431,59 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08dcea365e66c311</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f02d61ee29dd6bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist - Data Platforms - I&amp;D</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, BigQuery, Scala, Snowflake, Data Modeling, dbt, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Database and Applications Developer</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Lynker</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pascagoula, MS, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,19 +5816,19 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,147 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - App Reliability</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - EMC Life</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>EMC Insurance</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Family Dollar</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Chesapeake, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Security Automation Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>MarLabs</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c059189127bc5cc1</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,52 +573,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior . Net Backend Software Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
+          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
+          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Remote Snowflake Certified Architect / Senior Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MindBoard</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CNA National Warranty Corporation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Databricks, Scala, Snowflake, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02b34a3e260a27d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,29 +1606,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,77 +1641,77 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer – ServiceNow ITSM &amp; ITOM</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mapout Digital Solutions Inc,</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, ETL, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d775bd9dfd3ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,129 +3611,129 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,19 +3961,19 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,77 +4021,77 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Full Stack Engineer – POS</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,112 +4266,112 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – POS</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d55f6cd70406c7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,67 +4626,67 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730bcb3e79c6aa5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,94 +4696,94 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,24 +5001,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,67 +5151,67 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,102 +5221,102 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. System Engineer</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e1e1d56ef99307</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Data Scientist - Data Platforms - I&amp;D</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GCI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>RDS, Scala, Oracle, MySQL, MongoDB, NoSQL, Splunk, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=58ef90ed50c69d3c</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5605,286 +5605,6 @@
         </is>
       </c>
       <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Data Scientist - Data Platforms - I&amp;D</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Full Stack Application Developer</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Arctiq</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Database and Applications Developer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Lynker</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Pascagoula, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - App Reliability</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>MetLife</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, MongoDB, ETL, Splunk, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - EMC Life</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>EMC Insurance</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Family Dollar</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Chesapeake, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Remote Snowflake Certified Architect / Senior Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MindBoard</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, Time Travel</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,77 +811,77 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f6901b12a822f6</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -911,29 +911,29 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c449e7bee48aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ec255f7dfd4501</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b6758703ce1af49</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, SQL Server, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,129 +1371,129 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,29 +1501,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,207 +1756,207 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, MySQL, Splunk, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b210775ce96fe</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0424175a23c91455</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfb24ee33993b4d3</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbc9a5c20a1556b</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d995845b39a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa1f4b7324f011a4</t>
+          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,102 +2106,102 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65def939a6d6f9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2154128b023da7aa</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e42f400241a680</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,172 +2211,172 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bedbce0bdfe67c2</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a458738498ba664</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21475f2887c400b7</t>
+          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd2d3c5883bfed16</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e7db1f3e9fc085</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67bc95efc5566a38</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,207 +2421,207 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d36dfae3587b505c</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c53c3acfd1648584</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc2899f796a16fb</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab1e3f911c0a415</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Full Stack Engineer – POS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=694282a21f887d80</t>
+          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eee752d33d93ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0e642de58c95b9</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f637892c5403fa9</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9853ce2732f84a10</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47d50d062ae813bf</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49ee23c653fd5ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8278a573f0dad8</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df476be702e28761</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Data Engineer - DataOps</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=697cc31208b8ca3f</t>
+          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea2bc56a9e34beb</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Enterprise Operations Software Internship</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92c410b540d9e907</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,172 +2981,172 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a691585367c9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990326544cfad9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ce400ecee13b955</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71e23d6931640551</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99108deb158f7e9b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,84 +3156,84 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2176c06bd94e8f69</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db671c7409de21d4</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6066640ee62481e5</t>
+          <t>https://www.indeed.com/viewjob?jk=73529fee08b033be</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,15 +3243,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8850abbb9751d022</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=471ae09261cf084d</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,15 +3313,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dccc27b44783574a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,15 +3348,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3567f1e0f77dac43</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,15 +3383,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4cc1c3196bd4ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,15 +3418,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a3411d219babfd3</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9733ac8f8c23e449</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9be508658362ebf5</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f853f747d68926b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9dd345f23902fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dfe56f5a56c3183</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,49 +3681,49 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Data Scientist - Data Platforms - I&amp;D</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,102 +3786,102 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,1652 +3961,42 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Buildertrend</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Constant Contact</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Constant Contact</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>WhiteWater Express Car Wash</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>FIS</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>AWS Devops Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>MarLabs</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer – POS</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Confiz</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>NSD International</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Corning</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Newton, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>MeridianLink</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Blockchain Developer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Merck</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Rahway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Enterprise Operations Software Internship</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Spring, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Global Dining</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Cloud Engineer IV</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Availity, LLC.</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Snowflake AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Bridgewater, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Snowflake AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>HashiCorp Technical Consultant</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Arctiq</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Platform Engineer II</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Bestow</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>PDS Health</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>.NET Developer-Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>.NET Developer-Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>.NET Developer-Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Find the work that fits.</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>accrete</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Earth City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>General Mills</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Business Systems Analyst</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Foxconn Industrial Internet - FII</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Protera Health</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Troy, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>WA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Sr. DNS Engineer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>The Evolvers Group</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb25c410bfe57d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Data Scientist - Data Platforms - I&amp;D</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Full Stack Application Developer</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Arctiq</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>GCI</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, MySQL, MongoDB, NoSQL, Splunk, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58ef90ed50c69d3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Database and Applications Developer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Lynker</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Pascagoula, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Family Dollar</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Chesapeake, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Healthfirst</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7642aa199d34181</t>
+          <t>https://www.indeed.com/viewjob?jk=79d27925e100760a</t>
         </is>
       </c>
     </row>
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d27925e100760a</t>
+          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
         </is>
       </c>
     </row>
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363583288a17b581</t>
+          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer - Remote</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Altak Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6ed17078e339db4</t>
+          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Altak Group</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure</t>
+          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b6ef3996106ead</t>
+          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Blockchain data and/or NLP pipelines</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Foundation Software, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Strongsville, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Athena, Step Functions, S3, SQS, SNS, RDS, Hive, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52d29d5c7804bac2</t>
+          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Foundation Software, Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c3924b567192d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer, ITSM AI Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,77 +776,77 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1736ecfffb56a28</t>
+          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer, ITSM AI Platform</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb29d8a4e4f304ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e88a49966e5674a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3f6901b12a822f6</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3f6901b12a822f6</t>
+          <t>https://www.indeed.com/viewjob?jk=b0ec255f7dfd4501</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0ec255f7dfd4501</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Java Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Architect</t>
+          <t>Architect - Machine Learning and Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Coretek Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd64d36fc06c8909</t>
+          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Architect - Machine Learning and Data</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Coretek Services</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, PostgreSQL, Power BI, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef2d77f930831c</t>
+          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks Architect (Insurance Domain) - Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Saransh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,164 +1616,164 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EDP Cloud Systems Engineer – Washington, DC</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ff5e6c5e0c4cb98</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cyber Forward Deployed Engineer - Senior Consultant</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f37f98ae92022cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Snowflake, Databricks Lakehouse, SQL Server, MongoDB</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>WhiteWater Express Car Wash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe Experience Platform)</t>
+          <t>AAI Data Engineer – Enterprise Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
+          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer – POS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,112 +2376,112 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,94 +2491,94 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – POS</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,29 +2656,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Engineer - DataOps</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>DevXOps Platform Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Merck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,77 +2761,77 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - DataOps</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,94 +2876,94 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enterprise Operations Software Internship</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, RDS, Azure, Kafka, DynamoDB, Power BI, Splunk, AWS CodePipeline</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c8cc4ec9ed8337</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73529fee08b033be</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Business Systems Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Foxconn Industrial Internet - FII</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,94 +3471,94 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Business Systems Analyst</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Foxconn Industrial Internet - FII</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist - Data Platforms - I&amp;D</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Protera Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
+          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Full Stack Application Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
+          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. DNS Engineer</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Scientist - Data Platforms - I&amp;D</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend</t>
+          <t>Senior Java Full Stack Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CaseGuard</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,155 +3846,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Family Dollar</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Chesapeake, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Database and Applications Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Lynker</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Pascagoula, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>

--- a/results/job_matches_2026-08-12.xlsx
+++ b/results/job_matches_2026-08-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II, AWS Data Platform</t>
+          <t>Sr Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>VizyPay</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westbrook, ME, US USA</t>
+          <t>Waukee, IA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
+          <t>https://www.indeed.com/viewjob?jk=4d784aed378affa9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Engineer II, AWS Data Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westbrook, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
+          <t>https://www.indeed.com/viewjob?jk=12fffd8f7fd4e890</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ICON plc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
+          <t>https://www.indeed.com/viewjob?jk=c56d5a16ae0740c3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer (contract)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ICON plc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=77e55c51c6e20bd9</t>
         </is>
       </c>
     </row>
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0871e37a530ef61</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Senior AI Data Engineer (contract)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f64f4865300918b5</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Application Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>retail services &amp; systems</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Databricks, BigQuery, Spark, PySpark, Scala, Kafka, Snowflake, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,54 +1196,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a46eecd61e11e052</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9f2fec8662b4d8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772c80d310735c00</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Soteria</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,81 +1252,81 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a492248634dc4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
+          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Partner Solutions Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
+          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Science Engineer Internship</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6b0df3c9e5bfc9</t>
+          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Soteria</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43462e5c0569d38</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Architect (Insurance Domain) - Remote</t>
+          <t>Senior Specialist - Quality Engineering</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Saransh</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, HDFS, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,137 +1441,137 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=272dd0e98eb04f51</t>
+          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75eb200c811d29e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>AWS Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab6a03decb396a1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BAE Systems USA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589fe1b4025b2baa</t>
+          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Data Solutions &amp; Enablement Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, BigQuery, Scala, Kafka, Kafka Connect, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9002ba35285ed13</t>
+          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Center</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SpaceXAI</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Science Engineer Internship</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Verana Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880b15bbe3e3a364</t>
+          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer III-V</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vforce Infotech</t>
+          <t>Georgia System Operations Corporation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7686d5f40d3ad8</t>
+          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Specialist - Quality Engineering</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, PySpark, Snowflake</t>
+          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a578c93e384c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e306f479953cae8a</t>
+          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Engineer</t>
+          <t>Senior Full Stack Developer (Java, React, AWS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,102 +1791,102 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d33dd298324329e</t>
+          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Cloud Infrastructure and Integration Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Onyx Graphics, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e48e6726046f1b</t>
+          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Solutions &amp; Enablement Consultant</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, ETL</t>
+          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=574c41fe8815d88b</t>
+          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (AWS)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1024255b618280</t>
+          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Verana Health</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03eec9ffa29dd1d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III-V</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Georgia System Operations Corporation</t>
+          <t>MarLabs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86f2c7120d093631</t>
+          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>AdventHealth Corporate</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Altamonte Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, BigQuery, Scala, Kafka, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc63a70e65497f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Full Stack Engineer – POS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9a8d3217f1fd88</t>
+          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, React, AWS)</t>
+          <t>Data Engineer at a Major Japanese Bank 991394</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NSD International</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Scala, PostgreSQL, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e1e849982bafdc</t>
+          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure and Integration Engineer</t>
+          <t>Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Onyx Graphics, Inc.</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057a25cf24127b26</t>
+          <t>https://www.indeed.com/viewjob?jk=85217024f115b96c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe Experience Platform)</t>
+          <t>IT Manufacturing Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dentsu</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Newton, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,207 +2141,207 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00b472336df73668</t>
+          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b4a6b5b9f18e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>MeridianLink</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dea9ae7272713e5</t>
+          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Business Analytics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d6bd8fc3f8a77f</t>
+          <t>https://www.indeed.com/viewjob?jk=8abaf1ca57f1a8ac</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AAI Data Engineer – Enterprise Platform</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>hallmark health care solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ced02bbe46facd3c</t>
+          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MarLabs</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aa86ffff6ee80c1</t>
+          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AdventHealth Corporate</t>
+          <t>Mariner Wealth Advisors</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Altamonte Springs, FL, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, ETL, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,59 +2351,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf1a15fd8c75d64</t>
+          <t>https://www.indeed.com/viewjob?jk=7ceffe4425570abe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Engineer – POS</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, RDS, Scala, Kafka, DynamoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=693233f5a1305c78</t>
+          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer at a Major Japanese Bank 991394</t>
+          <t>Data Engineer - DataOps</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NSD International</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,172 +2421,172 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92dca2a30071c058</t>
+          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91304e0e40d6d369</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT Manufacturing Data Solutions Engineer</t>
+          <t>Senior Software Engineer - Global Dining</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Newton, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4258cff9137c8987</t>
+          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14de76ec36c970e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Snowflake AI Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MeridianLink</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, RDS, Scala, PostgreSQL, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73013c1070709d4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>HashiCorp Technical Consultant</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>hallmark health care solutions</t>
+          <t>Arctiq</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Blue Bell, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,137 +2596,137 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f17c7cef298683</t>
+          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Platform Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Bestow</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daf1ddd3f68c84f4</t>
+          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Engineer I, Business Analytics and Data Intelligence</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>PDS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae99be989417fae</t>
+          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938ccfc06579b5ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - DataOps</t>
+          <t>Senior Business Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>MedeAnalytics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, ETL, ELT, DataOps, CI/CD, Docker, Airflow</t>
+          <t>AWS, S3, RDS, Cloud Storage, Scala, Snowflake, Dimensional Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=159d4f00bd15e7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffa1810d5da5d3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevXOps Platform Engineer (Hybrid)</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Merck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rahway, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3f9585e32ad0f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, BigQuery, Scala, DynamoDB, NoSQL, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0ca6fcf446a943</t>
+          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Global Dining</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, MySQL, MongoDB, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a12a066e1d267b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2be9e1025f050f1</t>
+          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b792b16b24b1850f</t>
+          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Snowflake AI Data Engineer</t>
+          <t>.NET Developer-Software Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, ETL, ELT, Talend, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4dbc3396b3e9d4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HashiCorp Technical Consultant</t>
+          <t>Find the work that fits.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Arctiq</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Blue Bell, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fd373a29fef81c5</t>
+          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer II</t>
+          <t>Senior Associate, Data Scientist - PXT Analytics</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bestow</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431e5a9b7d2c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer I, Business Analytics and Data Intelligence</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PDS Health</t>
+          <t>Seneca Holdings, LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Microsoft SSIS, MLOps, Airflow, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, SQL Server, ETL, Power BI, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54ac8ecc98fde46e</t>
+          <t>https://www.indeed.com/viewjob?jk=d17896f3d07e4e12</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Forward Deployment Engineer - Cheminformatics &amp; AI Modelling</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, NoSQL, ETL, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,137 +3086,137 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c82553f05afcde</t>
+          <t>https://www.indeed.com/viewjob?jk=1dce2277438906ba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Machine Learning Engineer - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Mills</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2387b16461a952b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Protera Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761a68ed0406067e</t>
+          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6a8e88d647038c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Sr. DNS Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,172 +3226,172 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01da8d12018f03a0</t>
+          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. .NET Full Stack Developer-Software Engineer III</t>
+          <t>Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CaseGuard</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8f2df76176d2c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>.NET Developer-Software Engineer II</t>
+          <t>Data Scientist - Data Platforms - I&amp;D</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e28329fa974c80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Find the work that fits.</t>
+          <t>Automation Engineer - IT &amp; Business Systems</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156284a25afeae60</t>
+          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (AI/GenAI)</t>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cwill</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Associate, Data Scientist - PXT Analytics</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Family Dollar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chesapeake, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Apache Airflow</t>
+          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef867fd6329cd1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Remote</t>
+          <t>Database and Applications Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Mills</t>
+          <t>Lynker</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Pascagoula, MS, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,435 +3426,15 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5dbd615db9ede1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Business Systems Analyst</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Foxconn Industrial Internet - FII</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>S3, ECS, RDS, Hadoop, Hive, Spark, Kafka, ETL, Tableau, CI/CD</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d8d252c8ba7e84e</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Protera Health</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Troy, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, PostgreSQL, Data Modeling, dbt, Power BI, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a97fa47d3b2bf534</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>WA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0eb111e86cb26d</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Sr. DNS Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47fe0d3145b6d766</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer - Backend</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>CaseGuard</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, DynamoDB, NoSQL, Terraform</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7c9df2f7ea406e</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Scientist - Data Platforms - I&amp;D</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Vertex AI, Scala, MLOps, MLflow, Python, SQL, Scala</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61fbca34991c8dbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Full Stack Application Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Arctiq</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac1af4e0e0689</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Automation Engineer - IT &amp; Business Systems</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Jabil</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4beacc21980366f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Cwill</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Cary, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=117b4008b8891695</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Java Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e65800e07d6979c</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Family Dollar</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Chesapeake, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Oracle, ETL, ELT, Talend, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c4521197ca80202</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Database and Applications Developer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Lynker</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Pascagoula, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Oracle, SQL Server, PostgreSQL, ETL, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0637e6b70acc24b1</t>
         </is>
